--- a/data/input/planilhas_custos_ipca.xlsx
+++ b/data/input/planilhas_custos_ipca.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelsonthony/Dev/projects/trajectory-analysis/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D14E7B-BED3-9D48-8624-732FE49D7E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E542DAD-EF47-8B48-805A-C8DD0F6EBB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-360" yWindow="880" windowWidth="26800" windowHeight="18580" xr2:uid="{FF2BDEE5-ADAC-3545-8E07-87AA831F51D5}"/>
+    <workbookView xWindow="23440" yWindow="1440" windowWidth="26800" windowHeight="18580" activeTab="1" xr2:uid="{FF2BDEE5-ADAC-3545-8E07-87AA831F51D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
@@ -1056,6 +1056,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D525386-B4E4-3E4D-801F-722DBDFF5E44}">
   <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
